--- a/backend/data/financials_by_company/002026.SZ.xlsx
+++ b/backend/data/financials_by_company/002026.SZ.xlsx
@@ -692,658 +692,658 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>334328.212254</v>
+        <v>-1479624.6974</v>
       </c>
       <c r="C2" t="n">
-        <v>0.119154</v>
+        <v>0.10082</v>
       </c>
       <c r="D2" t="n">
-        <v>447453400.21</v>
+        <v>537036684.58</v>
       </c>
       <c r="E2" t="n">
-        <v>2805846.37</v>
+        <v>-14675959.67</v>
       </c>
       <c r="F2" t="n">
-        <v>2805846.37</v>
+        <v>-14675959.67</v>
       </c>
       <c r="G2" t="n">
-        <v>300026866.14</v>
+        <v>376265268.4</v>
       </c>
       <c r="H2" t="n">
-        <v>93473009.70999999</v>
+        <v>73324261.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1646010830.76</v>
+        <v>2589946091.64</v>
       </c>
       <c r="J2" t="n">
-        <v>450259246.58</v>
+        <v>522360724.91</v>
       </c>
       <c r="K2" t="n">
-        <v>356786236.87</v>
+        <v>449036463.21</v>
       </c>
       <c r="L2" t="n">
-        <v>6060885.51</v>
+        <v>16975316.86</v>
       </c>
       <c r="M2" t="n">
-        <v>13214546.54</v>
+        <v>6197633.76</v>
       </c>
       <c r="N2" t="n">
-        <v>22670992.72</v>
+        <v>24935087.94</v>
       </c>
       <c r="O2" t="n">
-        <v>297555347.982254</v>
+        <v>389461603.3726</v>
       </c>
       <c r="P2" t="n">
-        <v>300026866.14</v>
+        <v>376265268.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1936836753.22</v>
+        <v>2890592020.18</v>
       </c>
       <c r="R2" t="n">
-        <v>387077.85</v>
+        <v>1284083.04</v>
       </c>
       <c r="S2" t="n">
-        <v>342834594.02</v>
+        <v>438659167</v>
       </c>
       <c r="T2" t="n">
-        <v>447801293</v>
+        <v>427574169</v>
       </c>
       <c r="U2" t="n">
-        <v>447801293</v>
+        <v>422769964</v>
       </c>
       <c r="V2" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="W2" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="X2" t="n">
-        <v>300026866.14</v>
+        <v>376265268.4</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>300026866.14</v>
+        <v>376265268.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2606834.77</v>
+        <v>-21926717.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>302633700.91</v>
+        <v>398191986.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>302633700.91</v>
+        <v>398191986.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>40937989.42</v>
+        <v>44646843.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>343571690.33</v>
+        <v>442838829.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>737096.3100000001</v>
+        <v>4179662.45</v>
       </c>
       <c r="AG2" t="n">
-        <v>-15464066.95</v>
+        <v>-9836159.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>452800.87</v>
+        <v>-4956406.54</v>
       </c>
       <c r="AI2" t="n">
-        <v>367439.46</v>
+        <v>2660483.34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14643826.62</v>
+        <v>12132082.87</v>
       </c>
       <c r="AK2" t="n">
-        <v>6060885.51</v>
+        <v>16975316.86</v>
       </c>
       <c r="AL2" t="n">
-        <v>3395560.67</v>
+        <v>1762137.32</v>
       </c>
       <c r="AM2" t="n">
-        <v>13214546.54</v>
+        <v>6197633.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>22670992.72</v>
+        <v>24935087.94</v>
       </c>
       <c r="AO2" t="n">
-        <v>284060337.04</v>
+        <v>419118368.08</v>
       </c>
       <c r="AP2" t="n">
-        <v>290825922.46</v>
+        <v>300645928.54</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24488653.59</v>
+        <v>21686880.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>20419515.41</v>
+        <v>13033821.37</v>
       </c>
       <c r="AS2" t="n">
-        <v>20419515.41</v>
+        <v>13033821.37</v>
       </c>
       <c r="AT2" t="n">
-        <v>116274712.33</v>
+        <v>159488019.28</v>
       </c>
       <c r="AU2" t="n">
-        <v>57655391.35</v>
+        <v>58315376.05</v>
       </c>
       <c r="AV2" t="n">
-        <v>18459996.49</v>
+        <v>16384857.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>39195394.86</v>
+        <v>41930518.08</v>
       </c>
       <c r="AX2" t="n">
-        <v>387077.85</v>
+        <v>1284083.04</v>
       </c>
       <c r="AY2" t="n">
-        <v>574886259.5</v>
+        <v>719764296.62</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1646010830.76</v>
+        <v>2589946091.64</v>
       </c>
       <c r="BA2" t="n">
-        <v>2220897090.26</v>
+        <v>3309710388.26</v>
       </c>
       <c r="BB2" t="n">
-        <v>2220897090.26</v>
+        <v>3309710388.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-2670962.620516</v>
+        <v>-5535913.445611</v>
       </c>
       <c r="C3" t="n">
-        <v>0.097999</v>
+        <v>0.108109</v>
       </c>
       <c r="D3" t="n">
-        <v>327011653.36</v>
+        <v>402534086.96</v>
       </c>
       <c r="E3" t="n">
-        <v>-27254879.36</v>
+        <v>-51207012.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-27254879.36</v>
+        <v>-51207012.2</v>
       </c>
       <c r="G3" t="n">
-        <v>166392766.33</v>
+        <v>206382639.61</v>
       </c>
       <c r="H3" t="n">
-        <v>84274874.45999999</v>
+        <v>79002815.09999999</v>
       </c>
       <c r="I3" t="n">
-        <v>1923377241.73</v>
+        <v>1977390787.55</v>
       </c>
       <c r="J3" t="n">
-        <v>299756774</v>
+        <v>351327074.76</v>
       </c>
       <c r="K3" t="n">
-        <v>215481899.54</v>
+        <v>272324259.66</v>
       </c>
       <c r="L3" t="n">
-        <v>4123294.18</v>
+        <v>1045580.23</v>
       </c>
       <c r="M3" t="n">
-        <v>15998455.94</v>
+        <v>16766468.13</v>
       </c>
       <c r="N3" t="n">
-        <v>23362967.17</v>
+        <v>20636404.52</v>
       </c>
       <c r="O3" t="n">
-        <v>190976683.069484</v>
+        <v>252053738.364389</v>
       </c>
       <c r="P3" t="n">
-        <v>166392766.33</v>
+        <v>206382639.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2193908505.42</v>
+        <v>2253148371.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1466058.86</v>
+        <v>781323.28</v>
       </c>
       <c r="S3" t="n">
-        <v>200121895.2</v>
+        <v>255070142.21</v>
       </c>
       <c r="T3" t="n">
-        <v>449710179</v>
+        <v>439111999</v>
       </c>
       <c r="U3" t="n">
-        <v>449710179</v>
+        <v>439111999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="W3" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="X3" t="n">
-        <v>166392766.33</v>
+        <v>206382639.61</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>166392766.33</v>
+        <v>206382639.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>-13541413.66</v>
+        <v>-21547181.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>179934179.99</v>
+        <v>227929821.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>179934179.99</v>
+        <v>227929821.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>19549263.61</v>
+        <v>27627970.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>199483443.6</v>
+        <v>255557791.53</v>
       </c>
       <c r="AF3" t="n">
-        <v>-638451.6</v>
+        <v>487649.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>-24087888.65</v>
+        <v>-34378064.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>-555541.71</v>
+        <v>-944111.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>6627988.57</v>
+        <v>-7581510.89</v>
       </c>
       <c r="AJ3" t="n">
-        <v>18015441.79</v>
+        <v>42903686.44</v>
       </c>
       <c r="AK3" t="n">
-        <v>4123294.18</v>
+        <v>1045580.23</v>
       </c>
       <c r="AL3" t="n">
-        <v>3241217.05</v>
+        <v>2824356.16</v>
       </c>
       <c r="AM3" t="n">
-        <v>15998455.94</v>
+        <v>16766468.13</v>
       </c>
       <c r="AN3" t="n">
-        <v>23362967.17</v>
+        <v>20636404.52</v>
       </c>
       <c r="AO3" t="n">
-        <v>173342777.23</v>
+        <v>214028208.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>270531263.69</v>
+        <v>275757584.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14839259.85</v>
+        <v>20334175.19</v>
       </c>
       <c r="AR3" t="n">
-        <v>14889647.67</v>
+        <v>13683739.93</v>
       </c>
       <c r="AS3" t="n">
-        <v>14889647.67</v>
+        <v>13683739.93</v>
       </c>
       <c r="AT3" t="n">
-        <v>129718673.96</v>
+        <v>140035378.69</v>
       </c>
       <c r="AU3" t="n">
-        <v>51617235.65</v>
+        <v>43489778.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>19021097.32</v>
+        <v>14685214.74</v>
       </c>
       <c r="AW3" t="n">
-        <v>32596138.33</v>
+        <v>28804563.51</v>
       </c>
       <c r="AX3" t="n">
-        <v>1466058.86</v>
+        <v>781323.28</v>
       </c>
       <c r="AY3" t="n">
-        <v>443874040.92</v>
+        <v>489785793.23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1923377241.73</v>
+        <v>1977390787.55</v>
       </c>
       <c r="BA3" t="n">
-        <v>2367251282.65</v>
+        <v>2467176580.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>2367251282.65</v>
+        <v>2467176580.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-5535913.445611</v>
+        <v>-2670962.620516</v>
       </c>
       <c r="C4" t="n">
-        <v>0.108109</v>
+        <v>0.097999</v>
       </c>
       <c r="D4" t="n">
-        <v>402534086.96</v>
+        <v>327011653.36</v>
       </c>
       <c r="E4" t="n">
-        <v>-51207012.2</v>
+        <v>-27254879.36</v>
       </c>
       <c r="F4" t="n">
-        <v>-51207012.2</v>
+        <v>-27254879.36</v>
       </c>
       <c r="G4" t="n">
-        <v>206382639.61</v>
+        <v>166392766.33</v>
       </c>
       <c r="H4" t="n">
-        <v>79002815.09999999</v>
+        <v>84274874.45999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1977390787.55</v>
+        <v>1923377241.73</v>
       </c>
       <c r="J4" t="n">
-        <v>351327074.76</v>
+        <v>299756774</v>
       </c>
       <c r="K4" t="n">
-        <v>272324259.66</v>
+        <v>215481899.54</v>
       </c>
       <c r="L4" t="n">
-        <v>1045580.23</v>
+        <v>4123294.18</v>
       </c>
       <c r="M4" t="n">
-        <v>16766468.13</v>
+        <v>15998455.94</v>
       </c>
       <c r="N4" t="n">
-        <v>20636404.52</v>
+        <v>23362967.17</v>
       </c>
       <c r="O4" t="n">
-        <v>252053738.364389</v>
+        <v>190976683.069484</v>
       </c>
       <c r="P4" t="n">
-        <v>206382639.61</v>
+        <v>166392766.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>2253148371.95</v>
+        <v>2193908505.42</v>
       </c>
       <c r="R4" t="n">
-        <v>781323.28</v>
+        <v>1466058.86</v>
       </c>
       <c r="S4" t="n">
-        <v>255070142.21</v>
+        <v>200121895.2</v>
       </c>
       <c r="T4" t="n">
-        <v>439111999</v>
+        <v>449710179</v>
       </c>
       <c r="U4" t="n">
-        <v>439111999</v>
+        <v>449710179</v>
       </c>
       <c r="V4" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="W4" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="X4" t="n">
-        <v>206382639.61</v>
+        <v>166392766.33</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>206382639.61</v>
+        <v>166392766.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>-21547181.58</v>
+        <v>-13541413.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>227929821.19</v>
+        <v>179934179.99</v>
       </c>
       <c r="AC4" t="n">
-        <v>227929821.19</v>
+        <v>179934179.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>27627970.34</v>
+        <v>19549263.61</v>
       </c>
       <c r="AE4" t="n">
-        <v>255557791.53</v>
+        <v>199483443.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>487649.32</v>
+        <v>-638451.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>-34378064.2</v>
+        <v>-24087888.65</v>
       </c>
       <c r="AH4" t="n">
-        <v>-944111.35</v>
+        <v>-555541.71</v>
       </c>
       <c r="AI4" t="n">
-        <v>-7581510.89</v>
+        <v>6627988.57</v>
       </c>
       <c r="AJ4" t="n">
-        <v>42903686.44</v>
+        <v>18015441.79</v>
       </c>
       <c r="AK4" t="n">
-        <v>1045580.23</v>
+        <v>4123294.18</v>
       </c>
       <c r="AL4" t="n">
-        <v>2824356.16</v>
+        <v>3241217.05</v>
       </c>
       <c r="AM4" t="n">
-        <v>16766468.13</v>
+        <v>15998455.94</v>
       </c>
       <c r="AN4" t="n">
-        <v>20636404.52</v>
+        <v>23362967.17</v>
       </c>
       <c r="AO4" t="n">
-        <v>214028208.83</v>
+        <v>173342777.23</v>
       </c>
       <c r="AP4" t="n">
-        <v>275757584.4</v>
+        <v>270531263.69</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20334175.19</v>
+        <v>14839259.85</v>
       </c>
       <c r="AR4" t="n">
-        <v>13683739.93</v>
+        <v>14889647.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>13683739.93</v>
+        <v>14889647.67</v>
       </c>
       <c r="AT4" t="n">
-        <v>140035378.69</v>
+        <v>129718673.96</v>
       </c>
       <c r="AU4" t="n">
-        <v>43489778.25</v>
+        <v>51617235.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>14685214.74</v>
+        <v>19021097.32</v>
       </c>
       <c r="AW4" t="n">
-        <v>28804563.51</v>
+        <v>32596138.33</v>
       </c>
       <c r="AX4" t="n">
-        <v>781323.28</v>
+        <v>1466058.86</v>
       </c>
       <c r="AY4" t="n">
-        <v>489785793.23</v>
+        <v>443874040.92</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1977390787.55</v>
+        <v>1923377241.73</v>
       </c>
       <c r="BA4" t="n">
-        <v>2467176580.78</v>
+        <v>2367251282.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>2467176580.78</v>
+        <v>2367251282.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1479624.6974</v>
+        <v>334328.212254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.10082</v>
+        <v>0.119154</v>
       </c>
       <c r="D5" t="n">
-        <v>537036684.58</v>
+        <v>447453400.21</v>
       </c>
       <c r="E5" t="n">
-        <v>-14675959.67</v>
+        <v>2805846.37</v>
       </c>
       <c r="F5" t="n">
-        <v>-14675959.67</v>
+        <v>2805846.37</v>
       </c>
       <c r="G5" t="n">
-        <v>376265268.4</v>
+        <v>300026866.14</v>
       </c>
       <c r="H5" t="n">
-        <v>73324261.7</v>
+        <v>93473009.70999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2589946091.64</v>
+        <v>1646010830.76</v>
       </c>
       <c r="J5" t="n">
-        <v>522360724.91</v>
+        <v>450259246.58</v>
       </c>
       <c r="K5" t="n">
-        <v>449036463.21</v>
+        <v>356786236.87</v>
       </c>
       <c r="L5" t="n">
-        <v>16975316.86</v>
+        <v>6060885.51</v>
       </c>
       <c r="M5" t="n">
-        <v>6197633.76</v>
+        <v>13214546.54</v>
       </c>
       <c r="N5" t="n">
-        <v>24935087.94</v>
+        <v>22670992.72</v>
       </c>
       <c r="O5" t="n">
-        <v>389461603.3726</v>
+        <v>297555347.982254</v>
       </c>
       <c r="P5" t="n">
-        <v>376265268.4</v>
+        <v>300026866.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>2890592020.18</v>
+        <v>1936836753.22</v>
       </c>
       <c r="R5" t="n">
-        <v>1284083.04</v>
+        <v>387077.85</v>
       </c>
       <c r="S5" t="n">
-        <v>438659167</v>
+        <v>342834594.02</v>
       </c>
       <c r="T5" t="n">
-        <v>427574169</v>
+        <v>447801293</v>
       </c>
       <c r="U5" t="n">
-        <v>422769964</v>
+        <v>447801293</v>
       </c>
       <c r="V5" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="W5" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="X5" t="n">
-        <v>376265268.4</v>
+        <v>300026866.14</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>376265268.4</v>
+        <v>300026866.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>-21926717.93</v>
+        <v>-2606834.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>398191986.33</v>
+        <v>302633700.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>398191986.33</v>
+        <v>302633700.91</v>
       </c>
       <c r="AD5" t="n">
-        <v>44646843.12</v>
+        <v>40937989.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>442838829.45</v>
+        <v>343571690.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>4179662.45</v>
+        <v>737096.3100000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>-9836159.67</v>
+        <v>-15464066.95</v>
       </c>
       <c r="AH5" t="n">
-        <v>-4956406.54</v>
+        <v>452800.87</v>
       </c>
       <c r="AI5" t="n">
-        <v>2660483.34</v>
+        <v>367439.46</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12132082.87</v>
+        <v>14643826.62</v>
       </c>
       <c r="AK5" t="n">
-        <v>16975316.86</v>
+        <v>6060885.51</v>
       </c>
       <c r="AL5" t="n">
-        <v>1762137.32</v>
+        <v>3395560.67</v>
       </c>
       <c r="AM5" t="n">
-        <v>6197633.76</v>
+        <v>13214546.54</v>
       </c>
       <c r="AN5" t="n">
-        <v>24935087.94</v>
+        <v>22670992.72</v>
       </c>
       <c r="AO5" t="n">
-        <v>419118368.08</v>
+        <v>284060337.04</v>
       </c>
       <c r="AP5" t="n">
-        <v>300645928.54</v>
+        <v>290825922.46</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21686880.18</v>
+        <v>24488653.59</v>
       </c>
       <c r="AR5" t="n">
-        <v>13033821.37</v>
+        <v>20419515.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>13033821.37</v>
+        <v>20419515.41</v>
       </c>
       <c r="AT5" t="n">
-        <v>159488019.28</v>
+        <v>116274712.33</v>
       </c>
       <c r="AU5" t="n">
-        <v>58315376.05</v>
+        <v>57655391.35</v>
       </c>
       <c r="AV5" t="n">
-        <v>16384857.97</v>
+        <v>18459996.49</v>
       </c>
       <c r="AW5" t="n">
-        <v>41930518.08</v>
+        <v>39195394.86</v>
       </c>
       <c r="AX5" t="n">
-        <v>1284083.04</v>
+        <v>387077.85</v>
       </c>
       <c r="AY5" t="n">
-        <v>719764296.62</v>
+        <v>574886259.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2589946091.64</v>
+        <v>1646010830.76</v>
       </c>
       <c r="BA5" t="n">
-        <v>3309710388.26</v>
+        <v>2220897090.26</v>
       </c>
       <c r="BB5" t="n">
-        <v>3309710388.26</v>
+        <v>2220897090.26</v>
       </c>
     </row>
   </sheetData>
@@ -1739,898 +1739,898 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>445666839</v>
+        <v>440726384</v>
       </c>
       <c r="C2" t="n">
-        <v>445666839</v>
+        <v>440726384</v>
       </c>
       <c r="D2" t="n">
-        <v>559318007.53</v>
+        <v>308324375.88</v>
       </c>
       <c r="E2" t="n">
-        <v>3473193738</v>
+        <v>2937246901</v>
       </c>
       <c r="F2" t="n">
-        <v>4197450875.11</v>
+        <v>3399762285.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2135374837.05</v>
+        <v>2162722418.27</v>
       </c>
       <c r="H2" t="n">
-        <v>3473193738</v>
+        <v>2937246901</v>
       </c>
       <c r="I2" t="n">
-        <v>3056840.19</v>
+        <v>3926161.37</v>
       </c>
       <c r="J2" t="n">
-        <v>3644143322.34</v>
+        <v>3099651368.71</v>
       </c>
       <c r="K2" t="n">
-        <v>3644143322.34</v>
+        <v>3289651368.71</v>
       </c>
       <c r="L2" t="n">
-        <v>3665144624.57</v>
+        <v>3125881040.93</v>
       </c>
       <c r="M2" t="n">
-        <v>21001302.23</v>
+        <v>26229672.22</v>
       </c>
       <c r="N2" t="n">
-        <v>3644143322.34</v>
-      </c>
-      <c r="O2" t="n">
+        <v>3099651368.71</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>1046793912.07</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1374110896.92</v>
+      </c>
+      <c r="R2" t="n">
+        <v>440726384</v>
+      </c>
+      <c r="S2" t="n">
+        <v>440726384</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1737960523.47</v>
+      </c>
+      <c r="V2" t="n">
+        <v>255524952.99</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4808893.84</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>38963424.25</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>17826473.53</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>193926161.37</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3926161.37</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1482435570.48</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4441988.11</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>114398214.51</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>110110916.67</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1319033987.9</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>163935162.3</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>1485355057.66</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1423034105.67</v>
-      </c>
-      <c r="R2" t="n">
-        <v>445666839</v>
-      </c>
-      <c r="S2" t="n">
-        <v>445666839</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="AK2" t="n">
+        <v>50399545.43</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1104699280.17</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>4863841564.4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1218683575.65</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>60551865.71</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2222052.11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>36561317.01</v>
+      </c>
+      <c r="AR2" t="n">
         <v>0</v>
       </c>
-      <c r="U2" t="n">
-        <v>1443085678.87</v>
-      </c>
-      <c r="V2" t="n">
-        <v>63195319.64</v>
-      </c>
-      <c r="W2" t="n">
-        <v>4850749.31</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>25942360.21</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>29345369.93</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3056840.19</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3056840.19</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1379890359.23</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>7564175.46</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>556261167.34</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>553307552.77</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>759503417.3099999</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>99823783.69</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>9619955.460000001</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>35199182.7</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>614860495.46</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>5108230303.44</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1592965107.16</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>11090687.23</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>211624.88</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>27194934.42</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>156496162.82</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>156496162.82</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>236543782.63</v>
+        <v>215613890.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>125424210.6</v>
+        <v>158403945.02</v>
       </c>
       <c r="AV2" t="n">
-        <v>170949584.34</v>
+        <v>162404467.71</v>
       </c>
       <c r="AW2" t="n">
-        <v>167616944.86</v>
+        <v>132140261.48</v>
       </c>
       <c r="AX2" t="n">
-        <v>3332639.48</v>
+        <v>30264206.23</v>
       </c>
       <c r="AY2" t="n">
-        <v>865054120.24</v>
+        <v>582926037.6900001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-631469285.77</v>
+        <v>-448773396.29</v>
       </c>
       <c r="BA2" t="n">
-        <v>1496523406.01</v>
+        <v>1031699433.98</v>
       </c>
       <c r="BB2" t="n">
-        <v>18482761.95</v>
+        <v>41425628.62</v>
       </c>
       <c r="BC2" t="n">
-        <v>5960522.9</v>
+        <v>9294603.59</v>
       </c>
       <c r="BD2" t="n">
-        <v>863729390.88</v>
+        <v>667562030.66</v>
       </c>
       <c r="BE2" t="n">
-        <v>608350730.28</v>
+        <v>313417171.11</v>
       </c>
       <c r="BF2" t="n">
-        <v>3515265196.28</v>
+        <v>3645157988.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>250345001.75</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
+        <v>17689335.05</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
-        <v>45669664.86</v>
+        <v>62196060.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>575123762.87</v>
+        <v>792285022.26</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>255993209.47</v>
+        <v>268419451.97</v>
       </c>
       <c r="BN2" t="n">
-        <v>91538180.38</v>
+        <v>238998944.41</v>
       </c>
       <c r="BO2" t="n">
-        <v>227592373.02</v>
+        <v>284866625.88</v>
       </c>
       <c r="BP2" t="n">
-        <v>66819314.76</v>
+        <v>281984602.78</v>
       </c>
       <c r="BQ2" t="n">
-        <v>614215919.05</v>
+        <v>591025776.26</v>
       </c>
       <c r="BR2" t="n">
-        <v>-87083129.92</v>
+        <v>-89466428.20999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>701299048.97</v>
+        <v>680492204.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>1963091532.99</v>
+        <v>1899977191.65</v>
       </c>
       <c r="BU2" t="n">
-        <v>800670466.61</v>
+        <v>246385800</v>
       </c>
       <c r="BV2" t="n">
-        <v>1162421066.38</v>
+        <v>1653591391.65</v>
       </c>
       <c r="BW2" t="n">
-        <v>323964267.39</v>
+        <v>501378998.47</v>
       </c>
       <c r="BX2" t="n">
-        <v>838456798.99</v>
+        <v>1152212393.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>445550168</v>
+        <v>444884761</v>
       </c>
       <c r="C3" t="n">
-        <v>445550168</v>
+        <v>444884761</v>
       </c>
       <c r="D3" t="n">
-        <v>571578009.74</v>
+        <v>697388235.1799999</v>
       </c>
       <c r="E3" t="n">
-        <v>3242944298.82</v>
+        <v>3118280140.23</v>
       </c>
       <c r="F3" t="n">
-        <v>3981898895.89</v>
+        <v>3963835935.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1860871949.11</v>
+        <v>2080718067.82</v>
       </c>
       <c r="H3" t="n">
-        <v>3242944298.82</v>
+        <v>3118280140.23</v>
       </c>
       <c r="I3" t="n">
-        <v>6142334.42</v>
+        <v>1785221.41</v>
       </c>
       <c r="J3" t="n">
-        <v>3420823340.33</v>
+        <v>3271079592.11</v>
       </c>
       <c r="K3" t="n">
-        <v>3420823340.33</v>
+        <v>3271079592.11</v>
       </c>
       <c r="L3" t="n">
-        <v>3454209607.79</v>
+        <v>3307724445.91</v>
       </c>
       <c r="M3" t="n">
-        <v>33386267.46</v>
+        <v>36644853.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3420823340.33</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>3271079592.11</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1294776032.45</v>
+        <v>1168209329.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>1421804492.31</v>
+        <v>1414928547.04</v>
       </c>
       <c r="R3" t="n">
-        <v>445550168</v>
+        <v>444884761</v>
       </c>
       <c r="S3" t="n">
-        <v>445550168</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+        <v>444884761</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>1843878309.59</v>
+        <v>1742160384.76</v>
       </c>
       <c r="V3" t="n">
-        <v>68389933.5</v>
+        <v>62898575.35</v>
       </c>
       <c r="W3" t="n">
-        <v>6862436.39</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
+        <v>5275705.87</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>30237452.26</v>
+        <v>33935454.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>25147710.43</v>
+        <v>21902193.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>6142334.42</v>
+        <v>1785221.41</v>
       </c>
       <c r="AB3" t="n">
-        <v>6142334.42</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
+        <v>1785221.41</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>1775488376.09</v>
+        <v>1679261809.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>5870021.7</v>
+        <v>15336082.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>565435675.3200001</v>
+        <v>695603013.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>561075555.5599999</v>
+        <v>692756343.6900001</v>
       </c>
       <c r="AH3" t="n">
-        <v>1132367835.51</v>
+        <v>822793123.87</v>
       </c>
       <c r="AI3" t="n">
-        <v>139745261.72</v>
+        <v>136242463.57</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16800000</v>
+        <v>11132000</v>
       </c>
       <c r="AK3" t="n">
-        <v>23854136.77</v>
+        <v>32273089.08</v>
       </c>
       <c r="AL3" t="n">
-        <v>951968437.02</v>
+        <v>643145571.22</v>
       </c>
       <c r="AM3" t="n">
-        <v>5298087917.38</v>
+        <v>5049884830.67</v>
       </c>
       <c r="AN3" t="n">
-        <v>1661727592.18</v>
+        <v>1289904953.44</v>
       </c>
       <c r="AO3" t="n">
         <v>9509996.550000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>596296.79</v>
+        <v>1302303.79</v>
       </c>
       <c r="AQ3" t="n">
-        <v>31533071.63</v>
+        <v>28407000.87</v>
       </c>
       <c r="AR3" t="n">
-        <v>272577412.88</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>272577412.88</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>216727850.26</v>
+        <v>211406456.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>135186168.42</v>
+        <v>110641545.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>177879041.51</v>
+        <v>152799451.88</v>
       </c>
       <c r="AW3" t="n">
-        <v>174546402.03</v>
+        <v>149466812.4</v>
       </c>
       <c r="AX3" t="n">
         <v>3332639.48</v>
       </c>
       <c r="AY3" t="n">
-        <v>817717754.14</v>
+        <v>775838198.98</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-557095691.37</v>
+        <v>-525588846.87</v>
       </c>
       <c r="BA3" t="n">
-        <v>1374813445.51</v>
+        <v>1301427045.85</v>
       </c>
       <c r="BB3" t="n">
-        <v>86661349.09</v>
+        <v>120840337.29</v>
       </c>
       <c r="BC3" t="n">
-        <v>10694855.6</v>
+        <v>5263869.63</v>
       </c>
       <c r="BD3" t="n">
-        <v>757794967.5</v>
+        <v>726449740.96</v>
       </c>
       <c r="BE3" t="n">
-        <v>519662273.32</v>
+        <v>448873097.97</v>
       </c>
       <c r="BF3" t="n">
-        <v>3636360325.2</v>
+        <v>3759979877.23</v>
       </c>
       <c r="BG3" t="n">
-        <v>30113725.52</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
+        <v>29512396.27</v>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>43734965.76</v>
+        <v>52112217.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>555749989.47</v>
+        <v>687284053.5599999</v>
       </c>
       <c r="BL3" t="n">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>258270596.74</v>
+        <v>316963084.33</v>
       </c>
       <c r="BN3" t="n">
-        <v>99735262.59</v>
+        <v>124404042.63</v>
       </c>
       <c r="BO3" t="n">
-        <v>197744130.14</v>
+        <v>245916926.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>422949501.49</v>
+        <v>256493437.06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>500975982.58</v>
+        <v>451671571.33</v>
       </c>
       <c r="BR3" t="n">
-        <v>-86603144.69</v>
+        <v>-81906916.87</v>
       </c>
       <c r="BS3" t="n">
-        <v>587579127.27</v>
+        <v>533578488.2</v>
       </c>
       <c r="BT3" t="n">
-        <v>2082836160.38</v>
+        <v>2282906201.42</v>
       </c>
       <c r="BU3" t="n">
-        <v>678950553.29</v>
+        <v>672320000</v>
       </c>
       <c r="BV3" t="n">
-        <v>1403885607.09</v>
+        <v>1610586201.42</v>
       </c>
       <c r="BW3" t="n">
-        <v>541150436.92</v>
+        <v>559680934.73</v>
       </c>
       <c r="BX3" t="n">
-        <v>862735170.17</v>
+        <v>1050905266.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>444884761</v>
+        <v>445550168</v>
       </c>
       <c r="C4" t="n">
-        <v>444884761</v>
+        <v>445550168</v>
       </c>
       <c r="D4" t="n">
-        <v>697388235.1799999</v>
+        <v>571578009.74</v>
       </c>
       <c r="E4" t="n">
-        <v>3118280140.23</v>
+        <v>3242944298.82</v>
       </c>
       <c r="F4" t="n">
-        <v>3963835935.8</v>
+        <v>3981898895.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2080718067.82</v>
+        <v>1860871949.11</v>
       </c>
       <c r="H4" t="n">
-        <v>3118280140.23</v>
+        <v>3242944298.82</v>
       </c>
       <c r="I4" t="n">
-        <v>1785221.41</v>
+        <v>6142334.42</v>
       </c>
       <c r="J4" t="n">
-        <v>3271079592.11</v>
+        <v>3420823340.33</v>
       </c>
       <c r="K4" t="n">
-        <v>3271079592.11</v>
+        <v>3420823340.33</v>
       </c>
       <c r="L4" t="n">
-        <v>3307724445.91</v>
+        <v>3454209607.79</v>
       </c>
       <c r="M4" t="n">
-        <v>36644853.8</v>
+        <v>33386267.46</v>
       </c>
       <c r="N4" t="n">
-        <v>3271079592.11</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>3420823340.33</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>1168209329.33</v>
+        <v>1294776032.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>1414928547.04</v>
+        <v>1421804492.31</v>
       </c>
       <c r="R4" t="n">
-        <v>444884761</v>
+        <v>445550168</v>
       </c>
       <c r="S4" t="n">
-        <v>444884761</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>445550168</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
       <c r="U4" t="n">
-        <v>1742160384.76</v>
+        <v>1843878309.59</v>
       </c>
       <c r="V4" t="n">
-        <v>62898575.35</v>
+        <v>68389933.5</v>
       </c>
       <c r="W4" t="n">
-        <v>5275705.87</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>6862436.39</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
       <c r="Y4" t="n">
-        <v>33935454.52</v>
+        <v>30237452.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>21902193.55</v>
+        <v>25147710.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>1785221.41</v>
+        <v>6142334.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>1785221.41</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>6142334.42</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
       <c r="AD4" t="n">
-        <v>1679261809.41</v>
+        <v>1775488376.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>15336082.08</v>
+        <v>5870021.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>695603013.77</v>
+        <v>565435675.3200001</v>
       </c>
       <c r="AG4" t="n">
-        <v>692756343.6900001</v>
+        <v>561075555.5599999</v>
       </c>
       <c r="AH4" t="n">
-        <v>822793123.87</v>
+        <v>1132367835.51</v>
       </c>
       <c r="AI4" t="n">
-        <v>136242463.57</v>
+        <v>139745261.72</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11132000</v>
+        <v>16800000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32273089.08</v>
+        <v>23854136.77</v>
       </c>
       <c r="AL4" t="n">
-        <v>643145571.22</v>
+        <v>951968437.02</v>
       </c>
       <c r="AM4" t="n">
-        <v>5049884830.67</v>
+        <v>5298087917.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>1289904953.44</v>
+        <v>1661727592.18</v>
       </c>
       <c r="AO4" t="n">
         <v>9509996.550000001</v>
       </c>
       <c r="AP4" t="n">
-        <v>1302303.79</v>
+        <v>596296.79</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28407000.87</v>
+        <v>31533071.63</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>272577412.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>272577412.88</v>
       </c>
       <c r="AT4" t="n">
-        <v>211406456.17</v>
+        <v>216727850.26</v>
       </c>
       <c r="AU4" t="n">
-        <v>110641545.2</v>
+        <v>135186168.42</v>
       </c>
       <c r="AV4" t="n">
-        <v>152799451.88</v>
+        <v>177879041.51</v>
       </c>
       <c r="AW4" t="n">
-        <v>149466812.4</v>
+        <v>174546402.03</v>
       </c>
       <c r="AX4" t="n">
         <v>3332639.48</v>
       </c>
       <c r="AY4" t="n">
-        <v>775838198.98</v>
+        <v>817717754.14</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-525588846.87</v>
+        <v>-557095691.37</v>
       </c>
       <c r="BA4" t="n">
-        <v>1301427045.85</v>
+        <v>1374813445.51</v>
       </c>
       <c r="BB4" t="n">
-        <v>120840337.29</v>
+        <v>86661349.09</v>
       </c>
       <c r="BC4" t="n">
-        <v>5263869.63</v>
+        <v>10694855.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>726449740.96</v>
+        <v>757794967.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>448873097.97</v>
+        <v>519662273.32</v>
       </c>
       <c r="BF4" t="n">
-        <v>3759979877.23</v>
+        <v>3636360325.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>29512396.27</v>
-      </c>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
+        <v>30113725.52</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
       <c r="BJ4" t="n">
-        <v>52112217.59</v>
+        <v>43734965.76</v>
       </c>
       <c r="BK4" t="n">
-        <v>687284053.5599999</v>
+        <v>555749989.47</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>316963084.33</v>
+        <v>258270596.74</v>
       </c>
       <c r="BN4" t="n">
-        <v>124404042.63</v>
+        <v>99735262.59</v>
       </c>
       <c r="BO4" t="n">
-        <v>245916926.6</v>
+        <v>197744130.14</v>
       </c>
       <c r="BP4" t="n">
-        <v>256493437.06</v>
+        <v>422949501.49</v>
       </c>
       <c r="BQ4" t="n">
-        <v>451671571.33</v>
+        <v>500975982.58</v>
       </c>
       <c r="BR4" t="n">
-        <v>-81906916.87</v>
+        <v>-86603144.69</v>
       </c>
       <c r="BS4" t="n">
-        <v>533578488.2</v>
+        <v>587579127.27</v>
       </c>
       <c r="BT4" t="n">
-        <v>2282906201.42</v>
+        <v>2082836160.38</v>
       </c>
       <c r="BU4" t="n">
-        <v>672320000</v>
+        <v>678950553.29</v>
       </c>
       <c r="BV4" t="n">
-        <v>1610586201.42</v>
+        <v>1403885607.09</v>
       </c>
       <c r="BW4" t="n">
-        <v>559680934.73</v>
+        <v>541150436.92</v>
       </c>
       <c r="BX4" t="n">
-        <v>1050905266.69</v>
+        <v>862735170.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>440726384</v>
+        <v>445666839</v>
       </c>
       <c r="C5" t="n">
-        <v>440726384</v>
+        <v>445666839</v>
       </c>
       <c r="D5" t="n">
-        <v>308324375.88</v>
+        <v>559318007.53</v>
       </c>
       <c r="E5" t="n">
-        <v>2937246901</v>
+        <v>3473193738</v>
       </c>
       <c r="F5" t="n">
-        <v>3399762285.38</v>
+        <v>4197450875.11</v>
       </c>
       <c r="G5" t="n">
-        <v>2162722418.27</v>
+        <v>2135374837.05</v>
       </c>
       <c r="H5" t="n">
-        <v>2937246901</v>
+        <v>3473193738</v>
       </c>
       <c r="I5" t="n">
-        <v>3926161.37</v>
+        <v>3056840.19</v>
       </c>
       <c r="J5" t="n">
-        <v>3099651368.71</v>
+        <v>3644143322.34</v>
       </c>
       <c r="K5" t="n">
-        <v>3289651368.71</v>
+        <v>3644143322.34</v>
       </c>
       <c r="L5" t="n">
-        <v>3125881040.93</v>
+        <v>3665144624.57</v>
       </c>
       <c r="M5" t="n">
-        <v>26229672.22</v>
+        <v>21001302.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3099651368.71</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>3644143322.34</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>1046793912.07</v>
+        <v>1485355057.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>1374110896.92</v>
+        <v>1423034105.67</v>
       </c>
       <c r="R5" t="n">
-        <v>440726384</v>
+        <v>445666839</v>
       </c>
       <c r="S5" t="n">
-        <v>440726384</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>445666839</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
       <c r="U5" t="n">
-        <v>1737960523.47</v>
+        <v>1443085678.87</v>
       </c>
       <c r="V5" t="n">
-        <v>255524952.99</v>
+        <v>63195319.64</v>
       </c>
       <c r="W5" t="n">
-        <v>4808893.84</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>4850749.31</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
       <c r="Y5" t="n">
-        <v>38963424.25</v>
+        <v>25942360.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>17826473.53</v>
+        <v>29345369.93</v>
       </c>
       <c r="AA5" t="n">
-        <v>193926161.37</v>
+        <v>3056840.19</v>
       </c>
       <c r="AB5" t="n">
-        <v>3926161.37</v>
+        <v>3056840.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>190000000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1482435570.48</v>
+        <v>1379890359.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>4441988.11</v>
+        <v>7564175.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>114398214.51</v>
+        <v>556261167.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>110110916.67</v>
+        <v>553307552.77</v>
       </c>
       <c r="AH5" t="n">
-        <v>1319033987.9</v>
+        <v>759503417.3099999</v>
       </c>
       <c r="AI5" t="n">
-        <v>163935162.3</v>
+        <v>99823783.69</v>
       </c>
       <c r="AJ5" t="n">
+        <v>9619955.460000001</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>35199182.7</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>614860495.46</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5108230303.44</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1592965107.16</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>11090687.23</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>211624.88</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>27194934.42</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>156496162.82</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>156496162.82</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>236543782.63</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>125424210.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>170949584.34</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>167616944.86</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3332639.48</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>865054120.24</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-631469285.77</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1496523406.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>18482761.95</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5960522.9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>863729390.88</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>608350730.28</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3515265196.28</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>250345001.75</v>
+      </c>
+      <c r="BH5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="n">
-        <v>50399545.43</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1104699280.17</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>4863841564.4</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1218683575.65</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>60551865.71</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2222052.11</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>36561317.01</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="BI5" t="n">
         <v>0</v>
       </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>215613890.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>158403945.02</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>162404467.71</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>132140261.48</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>30264206.23</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>582926037.6900001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-448773396.29</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1031699433.98</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>41425628.62</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>9294603.59</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>667562030.66</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>313417171.11</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3645157988.75</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>17689335.05</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>62196060.75</v>
+        <v>45669664.86</v>
       </c>
       <c r="BK5" t="n">
-        <v>792285022.26</v>
+        <v>575123762.87</v>
       </c>
       <c r="BL5" t="n">
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>268419451.97</v>
+        <v>255993209.47</v>
       </c>
       <c r="BN5" t="n">
-        <v>238998944.41</v>
+        <v>91538180.38</v>
       </c>
       <c r="BO5" t="n">
-        <v>284866625.88</v>
+        <v>227592373.02</v>
       </c>
       <c r="BP5" t="n">
-        <v>281984602.78</v>
+        <v>66819314.76</v>
       </c>
       <c r="BQ5" t="n">
-        <v>591025776.26</v>
+        <v>614215919.05</v>
       </c>
       <c r="BR5" t="n">
-        <v>-89466428.20999999</v>
+        <v>-87083129.92</v>
       </c>
       <c r="BS5" t="n">
-        <v>680492204.47</v>
+        <v>701299048.97</v>
       </c>
       <c r="BT5" t="n">
-        <v>1899977191.65</v>
+        <v>1963091532.99</v>
       </c>
       <c r="BU5" t="n">
-        <v>246385800</v>
+        <v>800670466.61</v>
       </c>
       <c r="BV5" t="n">
-        <v>1653591391.65</v>
+        <v>1162421066.38</v>
       </c>
       <c r="BW5" t="n">
-        <v>501378998.47</v>
+        <v>323964267.39</v>
       </c>
       <c r="BX5" t="n">
-        <v>1152212393.18</v>
+        <v>838456798.99</v>
       </c>
     </row>
   </sheetData>
@@ -2896,590 +2896,590 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>173250679.86</v>
+        <v>292123156.75</v>
       </c>
       <c r="C2" t="n">
-        <v>-592771127.22</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>586000000</v>
+        <v>300000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-94101986.2</v>
+        <v>-149468622.1</v>
       </c>
       <c r="F2" t="n">
-        <v>838456798.99</v>
+        <v>1149260329.42</v>
       </c>
       <c r="G2" t="n">
-        <v>862735170.17</v>
+        <v>898610412.21</v>
       </c>
       <c r="H2" t="n">
-        <v>11706117.08</v>
+        <v>-16116214.95</v>
       </c>
       <c r="I2" t="n">
-        <v>-35984488.26</v>
+        <v>266766132.16</v>
       </c>
       <c r="J2" t="n">
-        <v>-26253603.39</v>
+        <v>90382150.25</v>
       </c>
       <c r="K2" t="n">
-        <v>93910213.59999999</v>
+        <v>-162017977.86</v>
       </c>
       <c r="L2" t="n">
-        <v>-81600889.77</v>
+        <v>-47599871.89</v>
       </c>
       <c r="M2" t="n">
-        <v>-6771127.22</v>
+        <v>300000000</v>
       </c>
       <c r="N2" t="n">
-        <v>-6771127.22</v>
+        <v>300000000</v>
       </c>
       <c r="O2" t="n">
-        <v>-592771127.22</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>586000000</v>
+        <v>300000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-277083550.93</v>
+        <v>-265207796.94</v>
       </c>
       <c r="R2" t="n">
-        <v>-183867771.4</v>
+        <v>-116835169.84</v>
       </c>
       <c r="S2" t="n">
-        <v>495797782.19</v>
+        <v>978264830.16</v>
       </c>
       <c r="T2" t="n">
-        <v>-679665553.59</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
+        <v>-1095100000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-93215779.53</v>
+        <v>-148372627.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>886206.67</v>
+        <v>1095995</v>
       </c>
       <c r="Z2" t="n">
-        <v>-94101986.2</v>
+        <v>-149468622.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>267352666.06</v>
+        <v>441591778.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>-96484198.86</v>
+        <v>-44489281.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>8535796.710000001</v>
+        <v>3930821.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>-325771010.6</v>
+        <v>484106006.59</v>
       </c>
       <c r="AE2" t="n">
-        <v>-19894525.65</v>
+        <v>-321039468.84</v>
       </c>
       <c r="AF2" t="n">
-        <v>240645540.68</v>
+        <v>-211486640.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1893101.37</v>
+        <v>24225788.61</v>
       </c>
       <c r="AH2" t="n">
-        <v>93473009.70999999</v>
+        <v>73324261.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>7820041.26</v>
+        <v>5342796.39</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85652968.45</v>
+        <v>67981465.31</v>
       </c>
       <c r="AK2" t="n">
-        <v>-50677822.82</v>
+        <v>-32756405.04</v>
       </c>
       <c r="AL2" t="n">
-        <v>708855.1</v>
+        <v>-4808245.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>302633700.91</v>
+        <v>398191986.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>267352666.06</v>
+        <v>441591778.85</v>
       </c>
       <c r="AO2" t="n">
-        <v>-20908545.96</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
+        <v>-26378729.94</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-1898433132.73</v>
+        <v>-2733380756.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>-65748957.12</v>
+        <v>-79130701.54000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>-435562983.57</v>
+        <v>-458047246.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1397121192.04</v>
+        <v>-2196202808.56</v>
       </c>
       <c r="AV2" t="n">
-        <v>2186694344.75</v>
+        <v>3201351265.19</v>
       </c>
       <c r="AW2" t="n">
-        <v>49981559.49</v>
+        <v>140114070.12</v>
       </c>
       <c r="AX2" t="n">
-        <v>2136712785.26</v>
+        <v>3061237195.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>150313766.26</v>
+        <v>94829933.68000001</v>
       </c>
       <c r="C3" t="n">
-        <v>-690090551</v>
+        <v>-317735025</v>
       </c>
       <c r="D3" t="n">
-        <v>557771127.22</v>
+        <v>707596000</v>
       </c>
       <c r="E3" t="n">
-        <v>-153818292.1</v>
+        <v>-178508058.45</v>
       </c>
       <c r="F3" t="n">
-        <v>862735170.17</v>
+        <v>1050905266.69</v>
       </c>
       <c r="G3" t="n">
-        <v>1050905266.69</v>
+        <v>1149260329.42</v>
       </c>
       <c r="H3" t="n">
-        <v>14538540.93</v>
+        <v>63389306.17</v>
       </c>
       <c r="I3" t="n">
-        <v>-202708637.45</v>
+        <v>-161744368.9</v>
       </c>
       <c r="J3" t="n">
-        <v>-80609069.14</v>
+        <v>161905385.55</v>
       </c>
       <c r="K3" t="n">
-        <v>100413310.03</v>
+        <v>-146394008.86</v>
       </c>
       <c r="L3" t="n">
-        <v>-37382955.39</v>
+        <v>-81561580.59</v>
       </c>
       <c r="M3" t="n">
-        <v>-132319423.78</v>
+        <v>389860975</v>
       </c>
       <c r="N3" t="n">
-        <v>-132319423.78</v>
+        <v>389860975</v>
       </c>
       <c r="O3" t="n">
-        <v>-690090551</v>
+        <v>-317735025</v>
       </c>
       <c r="P3" t="n">
-        <v>557771127.22</v>
+        <v>707596000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-426231626.67</v>
+        <v>-596987746.58</v>
       </c>
       <c r="R3" t="n">
-        <v>-275929567.31</v>
+        <v>-418549338</v>
       </c>
       <c r="S3" t="n">
-        <v>2718695426.73</v>
+        <v>3201824195</v>
       </c>
       <c r="T3" t="n">
-        <v>-2994624994.04</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
+        <v>-3620373533</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-150302059.36</v>
+        <v>-178438408.58</v>
       </c>
       <c r="Y3" t="n">
-        <v>3516232.74</v>
+        <v>69649.87</v>
       </c>
       <c r="Z3" t="n">
-        <v>-153818292.1</v>
+        <v>-178508058.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>304132058.36</v>
+        <v>273337992.13</v>
       </c>
       <c r="AB3" t="n">
-        <v>38639005.22</v>
+        <v>-20874917.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>119446.12</v>
+        <v>4235371.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>122182709.99</v>
+        <v>-284273465.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>130426508.66</v>
+        <v>110058724.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>-214089659.55</v>
+        <v>149104451.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>2407818.09</v>
+        <v>-45582900.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>84274874.45999999</v>
+        <v>79002815.09999999</v>
       </c>
       <c r="AI3" t="n">
-        <v>7392978.36</v>
+        <v>6577321.51</v>
       </c>
       <c r="AJ3" t="n">
-        <v>76881896.09999999</v>
+        <v>72425493.59</v>
       </c>
       <c r="AK3" t="n">
-        <v>-24029092.98</v>
+        <v>3543941.16</v>
       </c>
       <c r="AL3" t="n">
-        <v>-555541.71</v>
+        <v>-905774.15</v>
       </c>
       <c r="AM3" t="n">
-        <v>179934179.99</v>
+        <v>227929821.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>304132058.36</v>
+        <v>273337992.13</v>
       </c>
       <c r="AO3" t="n">
-        <v>-65604878.17</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
+        <v>-75718405.03</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-2239774574.44</v>
+        <v>-2541950070.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>-72833601.95</v>
+        <v>-75233010.02</v>
       </c>
       <c r="AT3" t="n">
-        <v>-377870407.02</v>
+        <v>-362853877.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1789070565.47</v>
+        <v>-2103863182.84</v>
       </c>
       <c r="AV3" t="n">
-        <v>2609511510.97</v>
+        <v>2891006467.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>176652281.1</v>
+        <v>170845132.98</v>
       </c>
       <c r="AX3" t="n">
-        <v>2432859229.87</v>
+        <v>2720161334.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>94829933.68000001</v>
+        <v>150313766.26</v>
       </c>
       <c r="C4" t="n">
-        <v>-317735025</v>
+        <v>-690090551</v>
       </c>
       <c r="D4" t="n">
-        <v>707596000</v>
+        <v>557771127.22</v>
       </c>
       <c r="E4" t="n">
-        <v>-178508058.45</v>
+        <v>-153818292.1</v>
       </c>
       <c r="F4" t="n">
+        <v>862735170.17</v>
+      </c>
+      <c r="G4" t="n">
         <v>1050905266.69</v>
       </c>
-      <c r="G4" t="n">
-        <v>1149260329.42</v>
-      </c>
       <c r="H4" t="n">
-        <v>63389306.17</v>
+        <v>14538540.93</v>
       </c>
       <c r="I4" t="n">
-        <v>-161744368.9</v>
+        <v>-202708637.45</v>
       </c>
       <c r="J4" t="n">
-        <v>161905385.55</v>
+        <v>-80609069.14</v>
       </c>
       <c r="K4" t="n">
-        <v>-146394008.86</v>
+        <v>100413310.03</v>
       </c>
       <c r="L4" t="n">
-        <v>-81561580.59</v>
+        <v>-37382955.39</v>
       </c>
       <c r="M4" t="n">
-        <v>389860975</v>
+        <v>-132319423.78</v>
       </c>
       <c r="N4" t="n">
-        <v>389860975</v>
+        <v>-132319423.78</v>
       </c>
       <c r="O4" t="n">
-        <v>-317735025</v>
+        <v>-690090551</v>
       </c>
       <c r="P4" t="n">
-        <v>707596000</v>
+        <v>557771127.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>-596987746.58</v>
+        <v>-426231626.67</v>
       </c>
       <c r="R4" t="n">
-        <v>-418549338</v>
+        <v>-275929567.31</v>
       </c>
       <c r="S4" t="n">
-        <v>3201824195</v>
+        <v>2718695426.73</v>
       </c>
       <c r="T4" t="n">
-        <v>-3620373533</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>-2994624994.04</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" t="n">
-        <v>-178438408.58</v>
+        <v>-150302059.36</v>
       </c>
       <c r="Y4" t="n">
-        <v>69649.87</v>
+        <v>3516232.74</v>
       </c>
       <c r="Z4" t="n">
-        <v>-178508058.45</v>
+        <v>-153818292.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>273337992.13</v>
+        <v>304132058.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>-20874917.5</v>
+        <v>38639005.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>4235371.66</v>
+        <v>119446.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>-284273465.08</v>
+        <v>122182709.99</v>
       </c>
       <c r="AE4" t="n">
-        <v>110058724.4</v>
+        <v>130426508.66</v>
       </c>
       <c r="AF4" t="n">
-        <v>149104451.52</v>
+        <v>-214089659.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>-45582900.74</v>
+        <v>2407818.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>79002815.09999999</v>
+        <v>84274874.45999999</v>
       </c>
       <c r="AI4" t="n">
-        <v>6577321.51</v>
+        <v>7392978.36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>72425493.59</v>
+        <v>76881896.09999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>3543941.16</v>
+        <v>-24029092.98</v>
       </c>
       <c r="AL4" t="n">
-        <v>-905774.15</v>
+        <v>-555541.71</v>
       </c>
       <c r="AM4" t="n">
-        <v>227929821.19</v>
+        <v>179934179.99</v>
       </c>
       <c r="AN4" t="n">
-        <v>273337992.13</v>
+        <v>304132058.36</v>
       </c>
       <c r="AO4" t="n">
-        <v>-75718405.03</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+        <v>-65604878.17</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-2541950070.74</v>
+        <v>-2239774574.44</v>
       </c>
       <c r="AS4" t="n">
-        <v>-75233010.02</v>
+        <v>-72833601.95</v>
       </c>
       <c r="AT4" t="n">
-        <v>-362853877.88</v>
+        <v>-377870407.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2103863182.84</v>
+        <v>-1789070565.47</v>
       </c>
       <c r="AV4" t="n">
-        <v>2891006467.9</v>
+        <v>2609511510.97</v>
       </c>
       <c r="AW4" t="n">
-        <v>170845132.98</v>
+        <v>176652281.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>2720161334.92</v>
+        <v>2432859229.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>292123156.75</v>
+        <v>173250679.86</v>
       </c>
       <c r="C5" t="n">
+        <v>-592771127.22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>586000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-94101986.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>838456798.99</v>
+      </c>
+      <c r="G5" t="n">
+        <v>862735170.17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11706117.08</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-35984488.26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-26253603.39</v>
+      </c>
+      <c r="K5" t="n">
+        <v>93910213.59999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-81600889.77</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-6771127.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-6771127.22</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-592771127.22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>586000000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-277083550.93</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-183867771.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>495797782.19</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-679665553.59</v>
+      </c>
+      <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-149468622.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1149260329.42</v>
-      </c>
-      <c r="G5" t="n">
-        <v>898610412.21</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-16116214.95</v>
-      </c>
-      <c r="I5" t="n">
-        <v>266766132.16</v>
-      </c>
-      <c r="J5" t="n">
-        <v>90382150.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-162017977.86</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-47599871.89</v>
-      </c>
-      <c r="M5" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-265207796.94</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-116835169.84</v>
-      </c>
-      <c r="S5" t="n">
-        <v>978264830.16</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1095100000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" t="n">
-        <v>-148372627.1</v>
+        <v>-93215779.53</v>
       </c>
       <c r="Y5" t="n">
-        <v>1095995</v>
+        <v>886206.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>-149468622.1</v>
+        <v>-94101986.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>441591778.85</v>
+        <v>267352666.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>-44489281.29</v>
+        <v>-96484198.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>3930821.46</v>
+        <v>8535796.710000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>484106006.59</v>
+        <v>-325771010.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>-321039468.84</v>
+        <v>-19894525.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>-211486640.5</v>
+        <v>240645540.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>24225788.61</v>
+        <v>1893101.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>73324261.7</v>
+        <v>93473009.70999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>5342796.39</v>
+        <v>7820041.26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67981465.31</v>
+        <v>85652968.45</v>
       </c>
       <c r="AK5" t="n">
-        <v>-32756405.04</v>
+        <v>-50677822.82</v>
       </c>
       <c r="AL5" t="n">
-        <v>-4808245.33</v>
+        <v>708855.1</v>
       </c>
       <c r="AM5" t="n">
-        <v>398191986.33</v>
+        <v>302633700.91</v>
       </c>
       <c r="AN5" t="n">
-        <v>441591778.85</v>
+        <v>267352666.06</v>
       </c>
       <c r="AO5" t="n">
-        <v>-26378729.94</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+        <v>-20908545.96</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
       <c r="AR5" t="n">
-        <v>-2733380756.4</v>
+        <v>-1898433132.73</v>
       </c>
       <c r="AS5" t="n">
-        <v>-79130701.54000001</v>
+        <v>-65748957.12</v>
       </c>
       <c r="AT5" t="n">
-        <v>-458047246.3</v>
+        <v>-435562983.57</v>
       </c>
       <c r="AU5" t="n">
-        <v>-2196202808.56</v>
+        <v>-1397121192.04</v>
       </c>
       <c r="AV5" t="n">
-        <v>3201351265.19</v>
+        <v>2186694344.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>140114070.12</v>
+        <v>49981559.49</v>
       </c>
       <c r="AX5" t="n">
-        <v>3061237195.07</v>
+        <v>2136712785.26</v>
       </c>
     </row>
   </sheetData>
@@ -4084,187 +4084,187 @@
       </c>
       <c r="DN1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EY1" t="inlineStr">
@@ -4369,34 +4369,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>12.94</v>
+        <v>11.99</v>
       </c>
       <c r="V2" t="n">
-        <v>12.71</v>
+        <v>11.95</v>
       </c>
       <c r="W2" t="n">
-        <v>12.28</v>
+        <v>11.22</v>
       </c>
       <c r="X2" t="n">
-        <v>12.98</v>
+        <v>12.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.94</v>
+        <v>11.99</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.71</v>
+        <v>11.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.28</v>
+        <v>11.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.98</v>
+        <v>12.01</v>
       </c>
       <c r="AC2" t="n">
         <v>0.13</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE2" t="n">
         <v>1764806400</v>
@@ -4408,34 +4408,34 @@
         <v>1.03</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.598</v>
+        <v>0.54</v>
       </c>
       <c r="AI2" t="n">
-        <v>20.81356</v>
+        <v>19.864408</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.92233</v>
+        <v>11.378641</v>
       </c>
       <c r="AK2" t="n">
-        <v>10236924</v>
+        <v>9891700</v>
       </c>
       <c r="AL2" t="n">
-        <v>10236924</v>
+        <v>9891700</v>
       </c>
       <c r="AM2" t="n">
-        <v>7377437</v>
+        <v>6785427</v>
       </c>
       <c r="AN2" t="n">
-        <v>8921183</v>
+        <v>5876610</v>
       </c>
       <c r="AO2" t="n">
-        <v>8921183</v>
+        <v>5876610</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.29</v>
+        <v>11.71</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.3</v>
+        <v>11.72</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4444,13 +4444,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>5409732096</v>
+        <v>5163034624</v>
       </c>
       <c r="AU2" t="n">
-        <v>5409732210</v>
+        <v>5281977948</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.28</v>
+        <v>11.22</v>
       </c>
       <c r="AW2" t="n">
         <v>17.29</v>
@@ -4462,19 +4462,19 @@
         <v>1.814595</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.786667</v>
+        <v>2.659588</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.9276</v>
+        <v>12.7644</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.3116</v>
+        <v>14.19435</v>
       </c>
       <c r="BC2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.005409583</v>
+        <v>0.0058381986</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4485,13 +4485,13 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>3686845952</v>
+        <v>3440147968</v>
       </c>
       <c r="BH2" t="n">
         <v>0.13239999</v>
       </c>
       <c r="BI2" t="n">
-        <v>272345655</v>
+        <v>272297197</v>
       </c>
       <c r="BJ2" t="n">
         <v>440531939</v>
@@ -4509,7 +4509,7 @@
         <v>8.77</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.4002279</v>
+        <v>1.3363739</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4541,16 +4541,16 @@
         <v>1368403200</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.899</v>
+        <v>1.772</v>
       </c>
       <c r="BZ2" t="n">
-        <v>14.797</v>
+        <v>13.807</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.047781587</v>
+        <v>0.008410453999999999</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CC2" t="n">
         <v>0.05</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>12.28</v>
+        <v>11.72</v>
       </c>
       <c r="CG2" t="n">
         <v>13</v>
@@ -4683,80 +4683,76 @@
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>SHANDONG WEIDA MACHINERY CO</t>
         </is>
       </c>
       <c r="DO2" t="n">
-        <v>1780038243</v>
-      </c>
-      <c r="DP2" t="inlineStr">
+        <v>-2.2518725</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>finmb_11369799</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DT2" t="n">
+      <c r="DV2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DV2" t="b">
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>SHANDONG WEIDA MACHINERY CO</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Shandong Weida Machinery Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
+      <c r="DY2" t="b">
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>7377437</v>
+        <v>6785427</v>
       </c>
       <c r="EA2" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.19455254</v>
+        <v>0.04456328</v>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>10.28 - 17.29</t>
+          <t>11.22 - 17.29</t>
         </is>
       </c>
       <c r="ED2" t="n">
-        <v>-5.010001</v>
+        <v>-5.5700006</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.2897629</v>
+        <v>-0.32215154</v>
       </c>
       <c r="EF2" t="n">
-        <v>4.7781587</v>
+        <v>0.8410454000000001</v>
       </c>
       <c r="EG2" t="n">
         <v>1618916340</v>
@@ -4771,16 +4767,16 @@
         <v>1.03</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.6476002</v>
+        <v>-1.0443993</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0.050094385</v>
+        <v>-0.08182126000000001</v>
       </c>
       <c r="EM2" t="n">
-        <v>-2.0316</v>
+        <v>-2.47435</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0.14195478</v>
+        <v>-0.17431936</v>
       </c>
       <c r="EO2" t="n">
         <v>15</v>
@@ -4788,33 +4784,37 @@
       <c r="EP2" t="n">
         <v>15</v>
       </c>
-      <c r="EQ2" t="b">
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ER2" t="n">
+        <v>1782111855</v>
+      </c>
+      <c r="ES2" t="b">
         <v>0</v>
       </c>
-      <c r="ER2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ES2" t="n">
+      <c r="ET2" t="n">
         <v>1090891800000</v>
       </c>
-      <c r="ET2" t="n">
-        <v>-0.6599998500000001</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>12.28 - 12.98</t>
-        </is>
+      <c r="EU2" t="n">
+        <v>-0.2699995</v>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
+          <t>11.22 - 12.01</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="EW2" t="n">
-        <v>-5.1004624</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>12.28</v>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>Shandong Weida Machinery Co., Ltd.</t>
+        </is>
       </c>
       <c r="EY2" t="inlineStr"/>
     </row>
